--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/81.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/81.xlsx
@@ -426,13 +426,13 @@
         <v>-1.411291827627829</v>
       </c>
       <c r="E2">
-        <v>-9.404397260286824</v>
+        <v>-5.350520914042344</v>
       </c>
       <c r="F2">
-        <v>-3.111078892756541</v>
+        <v>-1.624191711060138</v>
       </c>
       <c r="G2">
-        <v>-14.59980570644164</v>
+        <v>-10.55559349472534</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-1.045351163934257</v>
       </c>
       <c r="E3">
-        <v>-8.930338487267861</v>
+        <v>-6.039596161419504</v>
       </c>
       <c r="F3">
-        <v>-2.927468772823822</v>
+        <v>-1.220133972792206</v>
       </c>
       <c r="G3">
-        <v>-14.536458443015</v>
+        <v>-10.24406119498542</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-0.7552994603458799</v>
       </c>
       <c r="E4">
-        <v>-9.696945738130346</v>
+        <v>-5.318359691639869</v>
       </c>
       <c r="F4">
-        <v>-3.116131933913618</v>
+        <v>-1.302118323014676</v>
       </c>
       <c r="G4">
-        <v>-14.66473779988149</v>
+        <v>-10.19602083013359</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-0.588160778179981</v>
       </c>
       <c r="E5">
-        <v>-9.839248505347379</v>
+        <v>-6.616759230645107</v>
       </c>
       <c r="F5">
-        <v>-3.119044473701861</v>
+        <v>-1.632624491220636</v>
       </c>
       <c r="G5">
-        <v>-14.30910752299341</v>
+        <v>-9.993493991819987</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-0.5184907941264419</v>
       </c>
       <c r="E6">
-        <v>-10.62655993937293</v>
+        <v>-7.367974198355519</v>
       </c>
       <c r="F6">
-        <v>-2.748885186291291</v>
+        <v>-1.462567290365121</v>
       </c>
       <c r="G6">
-        <v>-14.04896243409596</v>
+        <v>-9.098166752223664</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-0.5324021252048867</v>
       </c>
       <c r="E7">
-        <v>-11.45055201286061</v>
+        <v>-7.921688829169404</v>
       </c>
       <c r="F7">
-        <v>-2.822078901635252</v>
+        <v>-1.276535024146616</v>
       </c>
       <c r="G7">
-        <v>-14.2139373322725</v>
+        <v>-9.058336003713565</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-0.6031823679487304</v>
       </c>
       <c r="E8">
-        <v>-11.83091213018687</v>
+        <v>-8.558052639097282</v>
       </c>
       <c r="F8">
-        <v>-2.979883720235961</v>
+        <v>-0.8935327285230421</v>
       </c>
       <c r="G8">
-        <v>-14.45849169693025</v>
+        <v>-9.181473686396407</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-0.7074779184430626</v>
       </c>
       <c r="E9">
-        <v>-13.27677236830388</v>
+        <v>-8.628515694656633</v>
       </c>
       <c r="F9">
-        <v>-2.514101013315827</v>
+        <v>-1.178773588370427</v>
       </c>
       <c r="G9">
-        <v>-13.86136351326704</v>
+        <v>-8.842221626922298</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-0.8183176083704818</v>
       </c>
       <c r="E10">
-        <v>-12.7103689533205</v>
+        <v>-10.14148791756731</v>
       </c>
       <c r="F10">
-        <v>-2.579937169388123</v>
+        <v>-1.010166858837212</v>
       </c>
       <c r="G10">
-        <v>-13.75991142387057</v>
+        <v>-8.777191096835663</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-0.9121826940920693</v>
       </c>
       <c r="E11">
-        <v>-12.77206035472699</v>
+        <v>-10.18280118593929</v>
       </c>
       <c r="F11">
-        <v>-2.162449938786006</v>
+        <v>-0.6951064292238514</v>
       </c>
       <c r="G11">
-        <v>-12.84828471617771</v>
+        <v>-7.756806659944224</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-0.9671397569459436</v>
       </c>
       <c r="E12">
-        <v>-14.23699452536431</v>
+        <v>-11.32447929648707</v>
       </c>
       <c r="F12">
-        <v>-2.024849001139577</v>
+        <v>-0.7015047390430746</v>
       </c>
       <c r="G12">
-        <v>-12.56463623724995</v>
+        <v>-7.459409862682393</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-0.9688786588790774</v>
       </c>
       <c r="E13">
-        <v>-14.27017918289252</v>
+        <v>-12.18135261974445</v>
       </c>
       <c r="F13">
-        <v>-1.635580934481228</v>
+        <v>-0.382980076951206</v>
       </c>
       <c r="G13">
-        <v>-12.00947651794282</v>
+        <v>-7.984405312193547</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-0.9136089936520139</v>
       </c>
       <c r="E14">
-        <v>-15.58881647223803</v>
+        <v>-12.99925842416582</v>
       </c>
       <c r="F14">
-        <v>-1.596761981251237</v>
+        <v>0.06481297508233116</v>
       </c>
       <c r="G14">
-        <v>-12.36678842088011</v>
+        <v>-6.874768367663652</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-0.8095904282383718</v>
       </c>
       <c r="E15">
-        <v>-15.76213928640761</v>
+        <v>-13.46609880961656</v>
       </c>
       <c r="F15">
-        <v>-1.088134455523508</v>
+        <v>0.7585416820678191</v>
       </c>
       <c r="G15">
-        <v>-11.32670024852421</v>
+        <v>-7.721251343126081</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-0.6770647118974168</v>
       </c>
       <c r="E16">
-        <v>-16.58136740523922</v>
+        <v>-13.39566292490126</v>
       </c>
       <c r="F16">
-        <v>-0.8655181713277655</v>
+        <v>0.604077669202601</v>
       </c>
       <c r="G16">
-        <v>-11.29440646593615</v>
+        <v>-7.241661437554522</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-0.5471971248497433</v>
       </c>
       <c r="E17">
-        <v>-17.62674751601389</v>
+        <v>-14.72715202348054</v>
       </c>
       <c r="F17">
-        <v>-0.5065319034461551</v>
+        <v>1.540147744979293</v>
       </c>
       <c r="G17">
-        <v>-10.83370983410388</v>
+        <v>-5.701610254964467</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-0.4559038277902795</v>
       </c>
       <c r="E18">
-        <v>-18.43601752050264</v>
+        <v>-16.1693849539174</v>
       </c>
       <c r="F18">
-        <v>-0.1001423109393428</v>
+        <v>1.879652468281864</v>
       </c>
       <c r="G18">
-        <v>-11.3567660816734</v>
+        <v>-6.901927038511176</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-0.4347888582435067</v>
       </c>
       <c r="E19">
-        <v>-18.76756974497422</v>
+        <v>-18.15640689289903</v>
       </c>
       <c r="F19">
-        <v>0.3195384365453875</v>
+        <v>2.007118330755041</v>
       </c>
       <c r="G19">
-        <v>-10.69752273327912</v>
+        <v>-5.154256561747256</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-0.5029509532963615</v>
       </c>
       <c r="E20">
-        <v>-19.81107959598373</v>
+        <v>-18.84310016294816</v>
       </c>
       <c r="F20">
-        <v>0.6426928440515026</v>
+        <v>2.070687245245875</v>
       </c>
       <c r="G20">
-        <v>-9.911086112354534</v>
+        <v>-4.728140723929968</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-0.663664515988017</v>
       </c>
       <c r="E21">
-        <v>-20.81629214231036</v>
+        <v>-18.89328924037517</v>
       </c>
       <c r="F21">
-        <v>1.268492938905223</v>
+        <v>2.183901874921289</v>
       </c>
       <c r="G21">
-        <v>-10.29714151615256</v>
+        <v>-5.330287535968346</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-0.9025784198149291</v>
       </c>
       <c r="E22">
-        <v>-20.91085573653854</v>
+        <v>-17.42639424049253</v>
       </c>
       <c r="F22">
-        <v>1.143545313336557</v>
+        <v>2.600101822579456</v>
       </c>
       <c r="G22">
-        <v>-10.08407211296846</v>
+        <v>-5.209932329167914</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-1.189654372501122</v>
       </c>
       <c r="E23">
-        <v>-22.35690617056386</v>
+        <v>-18.21946136498184</v>
       </c>
       <c r="F23">
-        <v>1.275906827160278</v>
+        <v>3.13152933270184</v>
       </c>
       <c r="G23">
-        <v>-10.30120038722159</v>
+        <v>-5.435821464984767</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-1.484823633307284</v>
       </c>
       <c r="E24">
-        <v>-22.99498174366664</v>
+        <v>-20.57841140268744</v>
       </c>
       <c r="F24">
-        <v>1.652896832174333</v>
+        <v>2.59893713801112</v>
       </c>
       <c r="G24">
-        <v>-10.11500090738778</v>
+        <v>-5.25261774043473</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-1.745889669888441</v>
       </c>
       <c r="E25">
-        <v>-22.40266640041137</v>
+        <v>-19.95375369806939</v>
       </c>
       <c r="F25">
-        <v>1.535699412026259</v>
+        <v>3.219359471685866</v>
       </c>
       <c r="G25">
-        <v>-10.36989932301169</v>
+        <v>-4.501011286363646</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-1.935828489298224</v>
       </c>
       <c r="E26">
-        <v>-22.57163282258557</v>
+        <v>-20.05944375293441</v>
       </c>
       <c r="F26">
-        <v>1.522485295216802</v>
+        <v>3.339128144252229</v>
       </c>
       <c r="G26">
-        <v>-10.01822127749196</v>
+        <v>-5.004931449798486</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-2.029386560149486</v>
       </c>
       <c r="E27">
-        <v>-22.82568021441588</v>
+        <v>-20.61488373234522</v>
       </c>
       <c r="F27">
-        <v>1.261569444152625</v>
+        <v>2.977557370073884</v>
       </c>
       <c r="G27">
-        <v>-9.944042701697596</v>
+        <v>-5.107144782596749</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-2.016823753699093</v>
       </c>
       <c r="E28">
-        <v>-23.53174176779581</v>
+        <v>-20.1193645210039</v>
       </c>
       <c r="F28">
-        <v>1.271685466875612</v>
+        <v>3.003243386499892</v>
       </c>
       <c r="G28">
-        <v>-9.662464673573847</v>
+        <v>-6.242992124943489</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-1.906024002833164</v>
       </c>
       <c r="E29">
-        <v>-22.67594622135226</v>
+        <v>-20.28785092493329</v>
       </c>
       <c r="F29">
-        <v>1.50950974821935</v>
+        <v>2.471045494692904</v>
       </c>
       <c r="G29">
-        <v>-9.69364940327481</v>
+        <v>-5.335806550631332</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-1.720186117363418</v>
       </c>
       <c r="E30">
-        <v>-21.77692186203149</v>
+        <v>-19.01812568334462</v>
       </c>
       <c r="F30">
-        <v>1.17131053194359</v>
+        <v>2.542218821941438</v>
       </c>
       <c r="G30">
-        <v>-9.738296985034175</v>
+        <v>-4.87183854090429</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-1.493786970739561</v>
       </c>
       <c r="E31">
-        <v>-22.50128297887641</v>
+        <v>-19.96474883296002</v>
       </c>
       <c r="F31">
-        <v>1.38463501898213</v>
+        <v>2.504640763080841</v>
       </c>
       <c r="G31">
-        <v>-9.764090667712969</v>
+        <v>-5.064150936503345</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-1.265743712439808</v>
       </c>
       <c r="E32">
-        <v>-21.89440859168649</v>
+        <v>-19.06225566254937</v>
       </c>
       <c r="F32">
-        <v>1.054803970209451</v>
+        <v>2.528945062678979</v>
       </c>
       <c r="G32">
-        <v>-9.981819405511484</v>
+        <v>-4.2523865663614</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-1.076326642039618</v>
       </c>
       <c r="E33">
-        <v>-21.23027165066956</v>
+        <v>-19.39609929486883</v>
       </c>
       <c r="F33">
-        <v>1.054475936717943</v>
+        <v>2.539230072352137</v>
       </c>
       <c r="G33">
-        <v>-9.83340647315624</v>
+        <v>-5.524017419281081</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-0.9603764598200099</v>
       </c>
       <c r="E34">
-        <v>-21.15288908682649</v>
+        <v>-18.5783972717778</v>
       </c>
       <c r="F34">
-        <v>1.021836604312836</v>
+        <v>2.420660875785027</v>
       </c>
       <c r="G34">
-        <v>-9.701767145412877</v>
+        <v>-5.462284516861688</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-0.9424831323713648</v>
       </c>
       <c r="E35">
-        <v>-21.20047429169909</v>
+        <v>-17.81551695502363</v>
       </c>
       <c r="F35">
-        <v>0.9745335121433735</v>
+        <v>2.325869137147874</v>
       </c>
       <c r="G35">
-        <v>-9.35694685295239</v>
+        <v>-5.259482055937089</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-1.033120887156243</v>
       </c>
       <c r="E36">
-        <v>-20.92410605148498</v>
+        <v>-18.33004670024915</v>
       </c>
       <c r="F36">
-        <v>1.076702690869859</v>
+        <v>2.462620998206433</v>
       </c>
       <c r="G36">
-        <v>-9.159666687912337</v>
+        <v>-4.735241287384606</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-1.229137428272657</v>
       </c>
       <c r="E37">
-        <v>-20.40320474333067</v>
+        <v>-18.00307729147332</v>
       </c>
       <c r="F37">
-        <v>0.9125136446957745</v>
+        <v>2.626836552137407</v>
       </c>
       <c r="G37">
-        <v>-9.067953264104297</v>
+        <v>-5.095706444240524</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-1.513016073618567</v>
       </c>
       <c r="E38">
-        <v>-20.65424975689389</v>
+        <v>-17.36777314446324</v>
       </c>
       <c r="F38">
-        <v>1.272126158333901</v>
+        <v>2.398778722472676</v>
       </c>
       <c r="G38">
-        <v>-9.626965137522216</v>
+        <v>-4.1856137076267</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-1.857114345953485</v>
       </c>
       <c r="E39">
-        <v>-19.75827758905429</v>
+        <v>-16.95100862458932</v>
       </c>
       <c r="F39">
-        <v>1.123223804211079</v>
+        <v>2.415044544794046</v>
       </c>
       <c r="G39">
-        <v>-9.08229548354063</v>
+        <v>-4.602535562634424</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-2.231094484092044</v>
       </c>
       <c r="E40">
-        <v>-19.41452112713203</v>
+        <v>-16.6628255956892</v>
       </c>
       <c r="F40">
-        <v>1.073044620419096</v>
+        <v>2.742486581977052</v>
       </c>
       <c r="G40">
-        <v>-8.729216356415023</v>
+        <v>-4.837037905044819</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-2.609751357530949</v>
       </c>
       <c r="E41">
-        <v>-19.29750083029982</v>
+        <v>-16.49817480924431</v>
       </c>
       <c r="F41">
-        <v>0.7705132477730776</v>
+        <v>2.460493750716044</v>
       </c>
       <c r="G41">
-        <v>-8.704781099461837</v>
+        <v>-4.721492969050533</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-2.97312045379329</v>
       </c>
       <c r="E42">
-        <v>-18.36723000032613</v>
+        <v>-16.54525282502805</v>
       </c>
       <c r="F42">
-        <v>1.026261742978591</v>
+        <v>2.393748875602877</v>
       </c>
       <c r="G42">
-        <v>-8.961323407087022</v>
+        <v>-4.942033713725491</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.308780014423663</v>
       </c>
       <c r="E43">
-        <v>-18.22815603507656</v>
+        <v>-15.46541102705501</v>
       </c>
       <c r="F43">
-        <v>0.9891807045596743</v>
+        <v>2.398061356301851</v>
       </c>
       <c r="G43">
-        <v>-8.877691631979896</v>
+        <v>-4.650044369593624</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-3.612355028128185</v>
       </c>
       <c r="E44">
-        <v>-17.76027862907807</v>
+        <v>-14.36457975205641</v>
       </c>
       <c r="F44">
-        <v>0.6293693827448754</v>
+        <v>2.140846650793382</v>
       </c>
       <c r="G44">
-        <v>-8.758865474426164</v>
+        <v>-3.097823136239588</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.884154703807522</v>
       </c>
       <c r="E45">
-        <v>-16.94728621895502</v>
+        <v>-14.36225211641647</v>
       </c>
       <c r="F45">
-        <v>0.9672952377777113</v>
+        <v>2.299724205180716</v>
       </c>
       <c r="G45">
-        <v>-8.579402342453895</v>
+        <v>-3.683097907019302</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-4.124584601441629</v>
       </c>
       <c r="E46">
-        <v>-17.36122044257414</v>
+        <v>-14.61749955385881</v>
       </c>
       <c r="F46">
-        <v>0.5507689133628415</v>
+        <v>2.128227301779134</v>
       </c>
       <c r="G46">
-        <v>-8.450168150113607</v>
+        <v>-3.64966225932856</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-4.332570325615904</v>
       </c>
       <c r="E47">
-        <v>-17.04363856041622</v>
+        <v>-14.60902677899046</v>
       </c>
       <c r="F47">
-        <v>0.7348917927178933</v>
+        <v>2.166005825551209</v>
       </c>
       <c r="G47">
-        <v>-8.121681778576036</v>
+        <v>-4.030585832607616</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-4.506331867349388</v>
       </c>
       <c r="E48">
-        <v>-16.8019222033088</v>
+        <v>-14.5461172180759</v>
       </c>
       <c r="F48">
-        <v>0.8494318102377865</v>
+        <v>1.848370001682544</v>
       </c>
       <c r="G48">
-        <v>-8.660435390085942</v>
+        <v>-2.898449551844609</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-4.644372244975894</v>
       </c>
       <c r="E49">
-        <v>-15.41832848279726</v>
+        <v>-13.15938526507705</v>
       </c>
       <c r="F49">
-        <v>0.6230224317046256</v>
+        <v>2.071634897554678</v>
       </c>
       <c r="G49">
-        <v>-7.938041651558593</v>
+        <v>-3.735859949695173</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-4.743957234030781</v>
       </c>
       <c r="E50">
-        <v>-15.33762654750657</v>
+        <v>-11.1639131935971</v>
       </c>
       <c r="F50">
-        <v>0.6720452146023004</v>
+        <v>1.810046412159428</v>
       </c>
       <c r="G50">
-        <v>-8.158162399873943</v>
+        <v>-4.204785885198536</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-4.800385140788576</v>
       </c>
       <c r="E51">
-        <v>-15.12237006402596</v>
+        <v>-11.18690425613405</v>
       </c>
       <c r="F51">
-        <v>0.3815831550150705</v>
+        <v>1.815901312962414</v>
       </c>
       <c r="G51">
-        <v>-8.331506053637847</v>
+        <v>-3.182294904065933</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-4.808732387939672</v>
       </c>
       <c r="E52">
-        <v>-14.33874933631666</v>
+        <v>-11.75370164835609</v>
       </c>
       <c r="F52">
-        <v>0.3118810082739089</v>
+        <v>1.725561220747906</v>
       </c>
       <c r="G52">
-        <v>-7.26283516027762</v>
+        <v>-2.765875075956804</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-4.764518767714033</v>
       </c>
       <c r="E53">
-        <v>-14.32822516272284</v>
+        <v>-11.65466392180834</v>
       </c>
       <c r="F53">
-        <v>0.231351271210755</v>
+        <v>2.047670228591688</v>
       </c>
       <c r="G53">
-        <v>-8.277500427990946</v>
+        <v>-3.846184462188382</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-4.66266269644768</v>
       </c>
       <c r="E54">
-        <v>-13.93115950478228</v>
+        <v>-10.28064792382302</v>
       </c>
       <c r="F54">
-        <v>0.4493510638706953</v>
+        <v>1.498848659745321</v>
       </c>
       <c r="G54">
-        <v>-7.745450352126986</v>
+        <v>-3.414825232319102</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-4.498787878292663</v>
       </c>
       <c r="E55">
-        <v>-13.28535835502242</v>
+        <v>-11.00155834347411</v>
       </c>
       <c r="F55">
-        <v>0.3720428476370286</v>
+        <v>1.52635211425307</v>
       </c>
       <c r="G55">
-        <v>-8.336585384611867</v>
+        <v>-3.997179715910909</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-4.269983657499273</v>
       </c>
       <c r="E56">
-        <v>-13.7173340190881</v>
+        <v>-9.340332938500312</v>
       </c>
       <c r="F56">
-        <v>0.4726762331987238</v>
+        <v>1.899917648423951</v>
       </c>
       <c r="G56">
-        <v>-8.003029525764955</v>
+        <v>-3.222555492600319</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-3.977933978071194</v>
       </c>
       <c r="E57">
-        <v>-12.83536389288022</v>
+        <v>-10.85203266021484</v>
       </c>
       <c r="F57">
-        <v>0.3704209042623472</v>
+        <v>1.854824640485158</v>
       </c>
       <c r="G57">
-        <v>-8.7089023137405</v>
+        <v>-3.475590174378458</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-3.627637438840489</v>
       </c>
       <c r="E58">
-        <v>-12.12018652132285</v>
+        <v>-10.29932335063066</v>
       </c>
       <c r="F58">
-        <v>0.2532922386087055</v>
+        <v>1.532298135470365</v>
       </c>
       <c r="G58">
-        <v>-8.492778093284555</v>
+        <v>-4.423115086542428</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-3.228084146214174</v>
       </c>
       <c r="E59">
-        <v>-11.93928757013844</v>
+        <v>-8.752210962176148</v>
       </c>
       <c r="F59">
-        <v>0.4546145103480833</v>
+        <v>1.972709605577555</v>
       </c>
       <c r="G59">
-        <v>-8.284653490990536</v>
+        <v>-4.806089423296137</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-2.791635291721437</v>
       </c>
       <c r="E60">
-        <v>-12.54906018069327</v>
+        <v>-9.181120849338638</v>
       </c>
       <c r="F60">
-        <v>0.1149151207058537</v>
+        <v>1.886834413664136</v>
       </c>
       <c r="G60">
-        <v>-8.825165837256305</v>
+        <v>-4.183779504774971</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-2.334119876270026</v>
       </c>
       <c r="E61">
-        <v>-11.98676409163485</v>
+        <v>-7.739816256073348</v>
       </c>
       <c r="F61">
-        <v>0.527187778507348</v>
+        <v>2.111323636557608</v>
       </c>
       <c r="G61">
-        <v>-8.507530465415819</v>
+        <v>-5.225508287910598</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-1.870532078102729</v>
       </c>
       <c r="E62">
-        <v>-12.18869327611088</v>
+        <v>-8.300386996534845</v>
       </c>
       <c r="F62">
-        <v>0.3844227984718672</v>
+        <v>2.2842734963837</v>
       </c>
       <c r="G62">
-        <v>-8.393964106021878</v>
+        <v>-4.769221617854216</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-1.414715915729639</v>
       </c>
       <c r="E63">
-        <v>-11.39108409219189</v>
+        <v>-6.436462566503719</v>
       </c>
       <c r="F63">
-        <v>0.2302536844020456</v>
+        <v>1.744938391034192</v>
       </c>
       <c r="G63">
-        <v>-9.051110753839668</v>
+        <v>-5.527551294900603</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-0.9811483651140299</v>
       </c>
       <c r="E64">
-        <v>-11.40084748215243</v>
+        <v>-8.515059306868459</v>
       </c>
       <c r="F64">
-        <v>0.3508407839623753</v>
+        <v>1.660690112699871</v>
       </c>
       <c r="G64">
-        <v>-8.962652301818597</v>
+        <v>-6.611384713087025</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-0.5851248464435975</v>
       </c>
       <c r="E65">
-        <v>-11.18992474829716</v>
+        <v>-8.720402960746272</v>
       </c>
       <c r="F65">
-        <v>0.1113034388296478</v>
+        <v>1.708707257570547</v>
       </c>
       <c r="G65">
-        <v>-9.497038607432883</v>
+        <v>-6.423830088749165</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-0.2391242545573156</v>
       </c>
       <c r="E66">
-        <v>-10.59688032072666</v>
+        <v>-8.405542691466959</v>
       </c>
       <c r="F66">
-        <v>0.2646400436596559</v>
+        <v>1.49100733391042</v>
       </c>
       <c r="G66">
-        <v>-9.448164812304954</v>
+        <v>-5.551369682200612</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>0.04764429281057742</v>
       </c>
       <c r="E67">
-        <v>-10.79817099036761</v>
+        <v>-8.243962210399273</v>
       </c>
       <c r="F67">
-        <v>0.424041954612962</v>
+        <v>1.595659958110499</v>
       </c>
       <c r="G67">
-        <v>-9.402112867718147</v>
+        <v>-6.257409812475689</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>0.2681183050195807</v>
       </c>
       <c r="E68">
-        <v>-10.09985312754079</v>
+        <v>-7.87990459950063</v>
       </c>
       <c r="F68">
-        <v>0.4343402181645654</v>
+        <v>1.642918318440211</v>
       </c>
       <c r="G68">
-        <v>-9.722117281524552</v>
+        <v>-6.322463311113239</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>0.4189200806163532</v>
       </c>
       <c r="E69">
-        <v>-11.28860925387231</v>
+        <v>-7.603989206687283</v>
       </c>
       <c r="F69">
-        <v>0.1956701737025691</v>
+        <v>1.88063656875639</v>
       </c>
       <c r="G69">
-        <v>-8.96228152378238</v>
+        <v>-6.346340760401318</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>0.501233580649569</v>
       </c>
       <c r="E70">
-        <v>-11.43852438589624</v>
+        <v>-7.673016735986202</v>
       </c>
       <c r="F70">
-        <v>0.2951910618423045</v>
+        <v>1.483353219108553</v>
       </c>
       <c r="G70">
-        <v>-9.245746254302809</v>
+        <v>-6.242664002787544</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>0.5202802679518947</v>
       </c>
       <c r="E71">
-        <v>-10.59304923171617</v>
+        <v>-8.420491184166279</v>
       </c>
       <c r="F71">
-        <v>0.1692709329427516</v>
+        <v>1.431934797681982</v>
       </c>
       <c r="G71">
-        <v>-9.562610539076825</v>
+        <v>-5.867997719022349</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>0.4822051255047805</v>
       </c>
       <c r="E72">
-        <v>-11.19472040227128</v>
+        <v>-8.130496765663084</v>
       </c>
       <c r="F72">
-        <v>0.1220539909831798</v>
+        <v>1.133144332227006</v>
       </c>
       <c r="G72">
-        <v>-9.514648923542422</v>
+        <v>-6.423948212725305</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>0.3944339900870509</v>
       </c>
       <c r="E73">
-        <v>-11.41977650350449</v>
+        <v>-7.945685212936049</v>
       </c>
       <c r="F73">
-        <v>-0.2204891839528606</v>
+        <v>1.421896641494858</v>
       </c>
       <c r="G73">
-        <v>-9.643364682876319</v>
+        <v>-6.97694888824632</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>0.2655659847871146</v>
       </c>
       <c r="E74">
-        <v>-10.93403426754573</v>
+        <v>-8.465871022197144</v>
       </c>
       <c r="F74">
-        <v>-0.07126625164515482</v>
+        <v>1.627943092532401</v>
       </c>
       <c r="G74">
-        <v>-9.117309398801465</v>
+        <v>-6.087439254474893</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>0.1042028653789849</v>
       </c>
       <c r="E75">
-        <v>-11.49096411490506</v>
+        <v>-7.841792962252076</v>
       </c>
       <c r="F75">
-        <v>0.03256214698913801</v>
+        <v>1.517694018159009</v>
       </c>
       <c r="G75">
-        <v>-8.820083225060724</v>
+        <v>-6.068673948376428</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-0.08243171881853541</v>
       </c>
       <c r="E76">
-        <v>-11.86039702445081</v>
+        <v>-9.241725416983291</v>
       </c>
       <c r="F76">
-        <v>0.02469265666254271</v>
+        <v>0.9824112861439968</v>
       </c>
       <c r="G76">
-        <v>-8.93604815741462</v>
+        <v>-6.114440426687564</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-0.2867492340990656</v>
       </c>
       <c r="E77">
-        <v>-11.56384537558451</v>
+        <v>-8.500201383649292</v>
       </c>
       <c r="F77">
-        <v>-0.1194432714245713</v>
+        <v>1.542899581491393</v>
       </c>
       <c r="G77">
-        <v>-8.689297014922818</v>
+        <v>-5.684305092459955</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-0.4999689191416151</v>
       </c>
       <c r="E78">
-        <v>-12.22035183789851</v>
+        <v>-9.721947443126693</v>
       </c>
       <c r="F78">
-        <v>-0.1317561244997831</v>
+        <v>1.195954462176876</v>
       </c>
       <c r="G78">
-        <v>-8.730423845948899</v>
+        <v>-6.100583828042028</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-0.7133890293781329</v>
       </c>
       <c r="E79">
-        <v>-12.20703359584195</v>
+        <v>-9.606349087132893</v>
       </c>
       <c r="F79">
-        <v>-0.1283134295737484</v>
+        <v>0.9289782751938174</v>
       </c>
       <c r="G79">
-        <v>-8.360229867169226</v>
+        <v>-5.53152485420909</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-0.9178413387632576</v>
       </c>
       <c r="E80">
-        <v>-14.10122634614034</v>
+        <v>-10.04280341199216</v>
       </c>
       <c r="F80">
-        <v>-0.338726205191448</v>
+        <v>1.213991334005432</v>
       </c>
       <c r="G80">
-        <v>-8.117429315434995</v>
+        <v>-5.223811896364365</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-1.105078323545345</v>
       </c>
       <c r="E81">
-        <v>-13.27545911084165</v>
+        <v>-10.16823308505661</v>
       </c>
       <c r="F81">
-        <v>-0.2485484729878882</v>
+        <v>0.7315037700404433</v>
       </c>
       <c r="G81">
-        <v>-8.274977168611734</v>
+        <v>-5.770532313820603</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-1.268899921453045</v>
       </c>
       <c r="E82">
-        <v>-14.23182753652156</v>
+        <v>-11.08269954074354</v>
       </c>
       <c r="F82">
-        <v>-0.4883177609933995</v>
+        <v>0.7394395297592625</v>
       </c>
       <c r="G82">
-        <v>-7.565983938933157</v>
+        <v>-5.073157889684021</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-1.407418609908998</v>
       </c>
       <c r="E83">
-        <v>-14.51899618724396</v>
+        <v>-12.84298984310913</v>
       </c>
       <c r="F83">
-        <v>-0.5266289250054739</v>
+        <v>0.8231642798950142</v>
       </c>
       <c r="G83">
-        <v>-8.151901829138522</v>
+        <v>-5.439007531118987</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-1.52266818342267</v>
       </c>
       <c r="E84">
-        <v>-16.11302356641794</v>
+        <v>-13.01216004661368</v>
       </c>
       <c r="F84">
-        <v>-0.4190554773431244</v>
+        <v>0.7519876391768694</v>
       </c>
       <c r="G84">
-        <v>-8.008286042703187</v>
+        <v>-5.079316742551098</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-1.620103492664187</v>
       </c>
       <c r="E85">
-        <v>-16.9310380542155</v>
+        <v>-13.05852256350421</v>
       </c>
       <c r="F85">
-        <v>-0.6036331304023131</v>
+        <v>0.8903299656488037</v>
       </c>
       <c r="G85">
-        <v>-7.971191832973664</v>
+        <v>-4.721722654559694</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-1.706454477702248</v>
       </c>
       <c r="E86">
-        <v>-17.67774719028828</v>
+        <v>-15.03390179581212</v>
       </c>
       <c r="F86">
-        <v>-0.4229007588269197</v>
+        <v>0.6020721917204234</v>
       </c>
       <c r="G86">
-        <v>-7.511266288207857</v>
+        <v>-4.475670412260054</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-1.789452227125599</v>
       </c>
       <c r="E87">
-        <v>-18.81587044874004</v>
+        <v>-15.93754972709472</v>
       </c>
       <c r="F87">
-        <v>-0.490807005038812</v>
+        <v>0.6900928552070932</v>
       </c>
       <c r="G87">
-        <v>-7.141538242889626</v>
+        <v>-4.934260499851166</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-1.875738309734599</v>
       </c>
       <c r="E88">
-        <v>-19.82654433471992</v>
+        <v>-17.28141514513697</v>
       </c>
       <c r="F88">
-        <v>-0.7436976327046675</v>
+        <v>0.7829785204504045</v>
       </c>
       <c r="G88">
-        <v>-7.327074915968428</v>
+        <v>-4.768279907266655</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-1.970643057592081</v>
       </c>
       <c r="E89">
-        <v>-21.04140258523166</v>
+        <v>-19.7470062172492</v>
       </c>
       <c r="F89">
-        <v>-1.112299589397975</v>
+        <v>0.6146509507319338</v>
       </c>
       <c r="G89">
-        <v>-7.344403047023856</v>
+        <v>-4.141596120406749</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-2.076661668735454</v>
       </c>
       <c r="E90">
-        <v>-22.87789351972432</v>
+        <v>-20.25205333790265</v>
       </c>
       <c r="F90">
-        <v>-0.7652848872216226</v>
+        <v>1.227581529615761</v>
       </c>
       <c r="G90">
-        <v>-7.742123193465709</v>
+        <v>-5.410930118234819</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-2.195162274520889</v>
       </c>
       <c r="E91">
-        <v>-24.81367124683515</v>
+        <v>-21.30855538084016</v>
       </c>
       <c r="F91">
-        <v>-0.8107730264115519</v>
+        <v>0.5241153638103646</v>
       </c>
       <c r="G91">
-        <v>-6.906730746874203</v>
+        <v>-4.997315734559015</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-2.323473168050048</v>
       </c>
       <c r="E92">
-        <v>-26.92673420287227</v>
+        <v>-24.07423031154468</v>
       </c>
       <c r="F92">
-        <v>-0.8344924986233129</v>
+        <v>0.2031213384907506</v>
       </c>
       <c r="G92">
-        <v>-7.942156303394137</v>
+        <v>-4.314486965595451</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-2.454346733640049</v>
       </c>
       <c r="E93">
-        <v>-28.21473636555589</v>
+        <v>-27.13934152905838</v>
       </c>
       <c r="F93">
-        <v>-1.217333262603341</v>
+        <v>0.4883108395591616</v>
       </c>
       <c r="G93">
-        <v>-7.303630587926196</v>
+        <v>-4.763003702999068</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.57517113010375</v>
       </c>
       <c r="E94">
-        <v>-29.99266733841836</v>
+        <v>-29.62069169071731</v>
       </c>
       <c r="F94">
-        <v>-0.9173002460441655</v>
+        <v>0.4406416089976612</v>
       </c>
       <c r="G94">
-        <v>-7.76191224069072</v>
+        <v>-4.561589198794113</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.672959670094703</v>
       </c>
       <c r="E95">
-        <v>-32.2361571385874</v>
+        <v>-32.67676860258571</v>
       </c>
       <c r="F95">
-        <v>-0.802893595676123</v>
+        <v>-0.02760300584359288</v>
       </c>
       <c r="G95">
-        <v>-7.941552558627199</v>
+        <v>-5.435929745296228</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-2.729406275882717</v>
       </c>
       <c r="E96">
-        <v>-34.51749366027554</v>
+        <v>-34.32858383857157</v>
       </c>
       <c r="F96">
-        <v>-1.198000824156806</v>
+        <v>-0.09572462758021302</v>
       </c>
       <c r="G96">
-        <v>-7.464282476698168</v>
+        <v>-5.354102642046796</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-2.735643730589853</v>
       </c>
       <c r="E97">
-        <v>-37.00948120737849</v>
+        <v>-35.95533849939898</v>
       </c>
       <c r="F97">
-        <v>-1.127938337595427</v>
+        <v>-0.4270558497193621</v>
       </c>
       <c r="G97">
-        <v>-8.172166653489652</v>
+        <v>-5.641652493408734</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-2.671521794119312</v>
       </c>
       <c r="E98">
-        <v>-39.76902005580261</v>
+        <v>-38.39620410342933</v>
       </c>
       <c r="F98">
-        <v>-1.069453113855573</v>
+        <v>-0.2526447497947318</v>
       </c>
       <c r="G98">
-        <v>-8.430487383200056</v>
+        <v>-5.491493951183865</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-2.546161769373321</v>
       </c>
       <c r="E99">
-        <v>-41.70414568265634</v>
+        <v>-41.51119193366351</v>
       </c>
       <c r="F99">
-        <v>-1.395695675039325</v>
+        <v>-0.75413174851033</v>
       </c>
       <c r="G99">
-        <v>-8.57494644357617</v>
+        <v>-5.557266037342934</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-2.336184136441104</v>
       </c>
       <c r="E100">
-        <v>-44.71755078395046</v>
+        <v>-43.80616142635175</v>
       </c>
       <c r="F100">
-        <v>-1.630759836196935</v>
+        <v>-0.8434893969851184</v>
       </c>
       <c r="G100">
-        <v>-8.766451658671601</v>
+        <v>-5.775188367213455</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-2.080152328838598</v>
       </c>
       <c r="E101">
-        <v>-47.24159766279071</v>
+        <v>-45.92391588146081</v>
       </c>
       <c r="F101">
-        <v>-1.422388986227136</v>
+        <v>-0.7591210053773915</v>
       </c>
       <c r="G101">
-        <v>-8.612811740372161</v>
+        <v>-6.259680417794824</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-1.721143899898455</v>
       </c>
       <c r="E102">
-        <v>-50.0004629007062</v>
+        <v>-49.72110473552851</v>
       </c>
       <c r="F102">
-        <v>-1.64175392836689</v>
+        <v>-1.058960183964312</v>
       </c>
       <c r="G102">
-        <v>-9.398910395476129</v>
+        <v>-5.472400522929457</v>
       </c>
     </row>
   </sheetData>
